--- a/Configs/arcane_config.xlsx
+++ b/Configs/arcane_config.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="34">
   <si>
     <t>id</t>
   </si>
@@ -108,9 +108,6 @@
     <t>Icon/sword-2-64</t>
   </si>
   <si>
-    <t>10104</t>
-  </si>
-  <si>
     <t>闪电网</t>
   </si>
   <si>
@@ -120,9 +117,6 @@
     <t>Icon/black-hole-64</t>
   </si>
   <si>
-    <t>20023</t>
-  </si>
-  <si>
     <t>风之诗</t>
   </si>
   <si>
@@ -130,9 +124,6 @@
   </si>
   <si>
     <t>Icon/plant-64</t>
-  </si>
-  <si>
-    <t>10138</t>
   </si>
   <si>
     <t>slot_ids</t>
@@ -151,14 +142,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -614,148 +598,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1112,6 +1096,9 @@
   <cols>
     <col min="3" max="3" width="46.375" customWidth="1"/>
     <col min="4" max="4" width="20.375" customWidth="1"/>
+    <col min="8" max="8" width="13.75" customWidth="1"/>
+    <col min="13" max="13" width="12.625" customWidth="1"/>
+    <col min="14" max="14" width="13.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -1239,8 +1226,8 @@
       <c r="L3" t="s">
         <v>22</v>
       </c>
-      <c r="M3" t="s">
-        <v>22</v>
+      <c r="M3">
+        <v>70010</v>
       </c>
       <c r="N3" t="s">
         <v>22</v>
@@ -1283,8 +1270,8 @@
       <c r="L4" t="s">
         <v>22</v>
       </c>
-      <c r="M4" t="s">
-        <v>26</v>
+      <c r="M4">
+        <v>70201</v>
       </c>
       <c r="N4" t="s">
         <v>22</v>
@@ -1295,13 +1282,13 @@
         <v>4003</v>
       </c>
       <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s">
         <v>27</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>28</v>
-      </c>
-      <c r="D5" t="s">
-        <v>29</v>
       </c>
       <c r="E5">
         <v>5000</v>
@@ -1330,8 +1317,8 @@
       <c r="M5" t="s">
         <v>22</v>
       </c>
-      <c r="N5" t="s">
-        <v>30</v>
+      <c r="N5">
+        <v>202003</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -1339,13 +1326,13 @@
         <v>4004</v>
       </c>
       <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" t="s">
         <v>31</v>
-      </c>
-      <c r="C6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" t="s">
-        <v>33</v>
       </c>
       <c r="E6">
         <v>5000</v>
@@ -1371,8 +1358,8 @@
       <c r="L6" t="s">
         <v>22</v>
       </c>
-      <c r="M6" t="s">
-        <v>34</v>
+      <c r="M6">
+        <v>40002</v>
       </c>
       <c r="N6" t="s">
         <v>22</v>
@@ -1395,7 +1382,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -1405,7 +1392,7 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/arcane_config.xlsx
+++ b/Configs/arcane_config.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="33">
   <si>
     <t>id</t>
   </si>
@@ -36,7 +36,7 @@
     <t>name</t>
   </si>
   <si>
-    <t>desList</t>
+    <t>des</t>
   </si>
   <si>
     <t>icon</t>
@@ -78,9 +78,6 @@
     <t>string</t>
   </si>
   <si>
-    <t>string[]</t>
-  </si>
-  <si>
     <t>float</t>
   </si>
   <si>
@@ -90,7 +87,7 @@
     <t>陨石术</t>
   </si>
   <si>
-    <t>召唤陨石轰击指定区域|持续造成火焰伤害</t>
+    <t>召唤陨石轰击指定区域，持续造成火焰伤害</t>
   </si>
   <si>
     <t>Icon/silver-ore-64</t>
@@ -102,7 +99,7 @@
     <t>寒冰术</t>
   </si>
   <si>
-    <t>在指定区域释放寒冰|造成冰霜伤害并冻结敌人2秒</t>
+    <t>在指定区域释放寒冰，造成冰霜伤害并冻结敌人2秒</t>
   </si>
   <si>
     <t>Icon/sword-2-64</t>
@@ -111,7 +108,7 @@
     <t>闪电网</t>
   </si>
   <si>
-    <t>在指定区域展开闪电网|造成雷电伤害并弹射3次</t>
+    <t>在指定区域展开闪电网，造成雷电伤害并弹射3次</t>
   </si>
   <si>
     <t>Icon/black-hole-64</t>
@@ -120,7 +117,7 @@
     <t>风之诗</t>
   </si>
   <si>
-    <t>唤起全屏风暴|造成风属性伤害并击退敌人</t>
+    <t>唤起全屏风暴，造成风属性伤害并击退敌人</t>
   </si>
   <si>
     <t>Icon/plant-64</t>
@@ -1153,7 +1150,7 @@
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
         <v>15</v>
@@ -1165,13 +1162,13 @@
         <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J2" t="s">
         <v>14</v>
@@ -1180,13 +1177,13 @@
         <v>14</v>
       </c>
       <c r="L2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -1194,13 +1191,13 @@
         <v>4001</v>
       </c>
       <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
         <v>19</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>20</v>
-      </c>
-      <c r="D3" t="s">
-        <v>21</v>
       </c>
       <c r="E3">
         <v>20000</v>
@@ -1224,13 +1221,13 @@
         <v>1</v>
       </c>
       <c r="L3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M3">
         <v>70010</v>
       </c>
       <c r="N3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -1238,13 +1235,13 @@
         <v>4002</v>
       </c>
       <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
         <v>23</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>24</v>
-      </c>
-      <c r="D4" t="s">
-        <v>25</v>
       </c>
       <c r="E4">
         <v>20000</v>
@@ -1268,13 +1265,13 @@
         <v>2</v>
       </c>
       <c r="L4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M4">
         <v>70201</v>
       </c>
       <c r="N4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -1282,13 +1279,13 @@
         <v>4003</v>
       </c>
       <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
         <v>26</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>27</v>
-      </c>
-      <c r="D5" t="s">
-        <v>28</v>
       </c>
       <c r="E5">
         <v>5000</v>
@@ -1312,10 +1309,10 @@
         <v>3</v>
       </c>
       <c r="L5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N5">
         <v>202003</v>
@@ -1326,13 +1323,13 @@
         <v>4004</v>
       </c>
       <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" t="s">
         <v>29</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>30</v>
-      </c>
-      <c r="D6" t="s">
-        <v>31</v>
       </c>
       <c r="E6">
         <v>5000</v>
@@ -1356,13 +1353,13 @@
         <v>4</v>
       </c>
       <c r="L6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M6">
         <v>40002</v>
       </c>
       <c r="N6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1382,17 +1379,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/arcane_config.xlsx
+++ b/Configs/arcane_config.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="arcane_config" sheetId="1" r:id="rId1"/>
-    <sheet name="arcane_meta" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="31">
   <si>
     <t>id</t>
   </si>
@@ -121,12 +120,6 @@
   </si>
   <si>
     <t>Icon/plant-64</t>
-  </si>
-  <si>
-    <t>slot_ids</t>
-  </si>
-  <si>
-    <t>4001|4002|4003|4004</t>
   </si>
 </sst>
 </file>
@@ -1366,34 +1359,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
-  <cols>
-    <col min="1" max="1" width="21.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
 </file>